--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,51 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2320,8 +2445,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2340,695 +2469,674 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전라도 산타령 — 민요채보-1/전라도 산타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">전라도 산타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="P3" s="15"/>
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">팔</t>
         </is>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="14"/>
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">빼</t>
         </is>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F4" s="14"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">봇</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L4" s="14"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="P5" s="14"/>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">빼</t>
         </is>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="F6" s="14"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">딜</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="P6" s="14"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="C7" s="19"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="14"/>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="P7" s="14"/>
+      <c r="Q7" s="19"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="F9" s="14"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K9" s="17"/>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="P9" s="14"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="5" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="19"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="K11" s="21"/>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="N11" s="14"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="F12" s="14"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="P12" s="14"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="2"/>
@@ -1134,13 +1134,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―南</t>
+          <t xml:space="preserve">姑|–南</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1213,13 +1213,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―潢</t>
+          <t xml:space="preserve">南|–潢</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1479,13 +1479,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I26" s="2"/>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I30" s="2"/>
@@ -1668,13 +1668,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―潢</t>
+          <t xml:space="preserve">南|–潢</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1708,13 +1708,13 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢|―</t>
+          <t xml:space="preserve">潢潢|–</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="3"/>
@@ -1787,13 +1787,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南|―</t>
+          <t xml:space="preserve">南南|–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -2026,13 +2026,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|―南</t>
+          <t xml:space="preserve">淋|–南</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2066,13 +2066,13 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―南</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2180,13 +2180,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―南</t>
+          <t xml:space="preserve">潢|–南</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2444,13 +2444,13 @@
       <c r="D4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="9"/>
@@ -2505,7 +2505,7 @@
       <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -2549,7 +2549,7 @@
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="C7" s="9"/>
@@ -2567,7 +2567,7 @@
       <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="G7" s="9"/>
@@ -2592,7 +2592,7 @@
       <c r="C8" s="13"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="10"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="10"/>
@@ -2628,7 +2628,7 @@
       <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -2639,7 +2639,7 @@
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -2663,7 +2663,7 @@
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2674,7 +2674,7 @@
       <c r="D10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E10" s="12"/>
@@ -2741,7 +2741,7 @@
       <c r="D12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -2813,13 +2813,13 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="10"/>

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2373,57 +2411,57 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">전라도 산타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">춤</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2431,70 +2469,70 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">께</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I4" s="9"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="E5" s="26"/>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2502,43 +2540,43 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 –南</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀고낫거</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">덩</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">미야</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -2546,37 +2584,37 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –南</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –南</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2584,75 +2622,75 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="26"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –潢</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내품안으</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –潢</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">산아지</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2660,111 +2698,111 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –南</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">팔을</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="E10" s="24"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G10" s="24"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="12"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="13"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
 –</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">들어</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구나</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2772,38 +2810,38 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2811,26 +2849,26 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -2396,20 +2396,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="I11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       <c r="E14" s="27"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="27"/>

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -2409,7 +2409,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="58.2" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="58.2" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="58.2" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="58.2" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="55.19" customHeight="1">
+    <row r="6" ht="58.2" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2548,7 +2548,10 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">놀고낫거</t>
+          <t xml:space="preserve">놀
+고
+낫
+거</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -2568,7 +2571,8 @@
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">미야</t>
+          <t xml:space="preserve">미
+야</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -2582,7 +2586,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="55.19" customHeight="1">
+    <row r="7" ht="58.2" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2620,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="55.19" customHeight="1">
+    <row r="8" ht="58.2" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -2651,7 +2655,7 @@
       </c>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" ht="55.19" customHeight="1">
+    <row r="9" ht="58.2" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2671,7 +2675,10 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">내품안으</t>
+          <t xml:space="preserve">내
+품
+안
+으</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -2682,7 +2689,9 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">산아지</t>
+          <t xml:space="preserve">산
+아
+지</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -2696,7 +2705,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="55.19" customHeight="1">
+    <row r="10" ht="58.2" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2706,7 +2715,8 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔을</t>
+          <t xml:space="preserve">팔
+을</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -2729,7 +2739,7 @@
       </c>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="55.19" customHeight="1">
+    <row r="11" ht="58.2" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2764,7 +2774,7 @@
       </c>
       <c r="I11" s="26"/>
     </row>
-    <row r="12" ht="55.19" customHeight="1">
+    <row r="12" ht="58.2" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2784,7 +2794,8 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">들어</t>
+          <t xml:space="preserve">들
+어</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -2794,7 +2805,8 @@
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">구나</t>
+          <t xml:space="preserve">구
+나</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -2808,7 +2820,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="55.19" customHeight="1">
+    <row r="13" ht="58.2" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2847,7 +2859,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="55.19" customHeight="1">
+    <row r="14" ht="58.2" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -231,6 +236,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2431,7 +2451,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
@@ -2441,7 +2461,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">춤</t>
         </is>
@@ -2451,7 +2471,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2461,7 +2481,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2474,7 +2494,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">께</t>
         </is>
@@ -2485,19 +2505,19 @@
 –</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" ht="58.2" customHeight="1">
       <c r="A5" s="0"/>
@@ -2506,7 +2526,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -2516,13 +2536,13 @@
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -2532,7 +2552,7 @@
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2546,7 +2566,7 @@
 –南</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">놀
 고
@@ -2559,7 +2579,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">덩</t>
         </is>
@@ -2569,7 +2589,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">미
 야</t>
@@ -2580,7 +2600,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -2594,14 +2614,14 @@
 –南</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -2612,13 +2632,13 @@
 –南</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2631,19 +2651,19 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2653,7 +2673,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" ht="58.2" customHeight="1">
       <c r="A9" s="0"/>
@@ -2662,7 +2682,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -2673,7 +2693,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">내
 품
@@ -2687,7 +2707,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">산
 아
@@ -2699,7 +2719,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2713,7 +2733,7 @@
 –南</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">팔
 을</t>
@@ -2725,19 +2745,19 @@
 –</t>
         </is>
       </c>
-      <c r="E10" s="24"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="24"/>
+      <c r="G10" s="29"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="24"/>
+      <c r="I10" s="29"/>
     </row>
     <row r="11" ht="58.2" customHeight="1">
       <c r="A11" s="0"/>
@@ -2746,7 +2766,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -2756,13 +2776,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -2772,7 +2792,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="31"/>
     </row>
     <row r="12" ht="58.2" customHeight="1">
       <c r="A12" s="0"/>
@@ -2781,7 +2801,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -2792,7 +2812,7 @@
 –</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">들
 어</t>
@@ -2803,7 +2823,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">구
 나</t>
@@ -2814,7 +2834,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2827,7 +2847,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -2837,7 +2857,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -2847,13 +2867,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2866,21 +2886,21 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="27"/>
+      <c r="I14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,31 +221,19 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -359,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
@@ -383,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -393,11 +376,7 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 26%</t>
-        </is>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -423,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄 양식, 위에 줄 번호(오른쪽 1), 왼쪽에 정간 번호 1~12(단독), 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백에 제목 "전라도 산타령" 세로쓰기. 가장 오른쪽 인쇄 열(번호 1)은 비어 있어 내용 있는 첫 열을 줄1로 셈. 많은 율명 오른쪽에 닫는 곡선 ) 모양 요성 표시가 있는데 기호표에 없어 율명에서 빼고 비고로 남김(너무 흔해 여기 총괄 기록). AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
@@ -650,12 +629,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -685,12 +664,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃^</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃^</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -700,7 +679,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃 오른쪽 ) 요성</t>
+          <t xml:space="preserve">氵 없는 黃으로 보임</t>
         </is>
       </c>
       <c r="K4" s="2"/>
@@ -767,12 +746,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -878,22 +857,18 @@
       <c r="F9" s="2">
         <v>3</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 ) 요성</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="2"/>
     </row>
     <row r="10">
@@ -917,22 +892,18 @@
       <c r="F10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 ) 요성</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11">
@@ -1108,26 +1079,22 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 ) 요성</t>
-        </is>
-      </c>
+      <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
     <row r="16">
@@ -1163,7 +1130,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미야</t>
+          <t xml:space="preserve">디</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1201,7 +1168,11 @@
 –南</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
@@ -1226,26 +1197,22 @@
       <c r="F18" s="2">
         <v>2</v>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 ) 요성</t>
-        </is>
-      </c>
+      <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
     <row r="19">
@@ -1282,7 +1249,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">산아지</t>
+          <t xml:space="preserve">산아</t>
         </is>
       </c>
       <c r="J19" s="4"/>
@@ -1311,18 +1278,22 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I20" s="3"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢 ) 요성</t>
+          <t xml:space="preserve">潢 둘레에 점선 테두리</t>
         </is>
       </c>
       <c r="K20" s="2"/>
@@ -1348,22 +1319,26 @@
       <c r="F21" s="2">
         <v>3</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="J21" s="4"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑 아래 물결선</t>
+        </is>
+      </c>
       <c r="K21" s="2"/>
     </row>
     <row r="22">
@@ -1399,7 +1374,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구나</t>
+          <t xml:space="preserve">구</t>
         </is>
       </c>
       <c r="J22" s="4"/>
@@ -1436,7 +1411,11 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I23" s="2"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
@@ -1496,22 +1475,26 @@
       <c r="F25" s="2">
         <v>1</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">춤</t>
         </is>
       </c>
-      <c r="J25" s="4"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 춤/춥?</t>
+        </is>
+      </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1537,16 +1520,19 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|–</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-–</t>
-        </is>
-      </c>
-      <c r="I26" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
@@ -1573,18 +1559,18 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃^</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃^</t>
         </is>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃 ) 요성</t>
+          <t xml:space="preserve">氵 없는 黃으로 보임</t>
         </is>
       </c>
       <c r="K27" s="2"/>
@@ -1651,13 +1637,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1737,7 +1722,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">내품안으</t>
+          <t xml:space="preserve">내품</t>
         </is>
       </c>
       <c r="J31" s="4"/>
@@ -1764,23 +1749,23 @@
       <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢|–</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 두 개</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안으</t>
+        </is>
+      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1804,22 +1789,22 @@
       <c r="F33" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 ) 요성</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로</t>
+        </is>
+      </c>
+      <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
     <row r="34">
@@ -1996,26 +1981,22 @@
       <c r="F38" s="2">
         <v>1</v>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">께</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 께/게?</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게</t>
+        </is>
+      </c>
+      <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
     <row r="39">
@@ -2039,26 +2020,22 @@
       <c r="F39" s="2">
         <v>1</v>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 ) 요성</t>
-        </is>
-      </c>
+      <c r="J39" s="4"/>
       <c r="K39" s="2"/>
     </row>
     <row r="40">
@@ -2084,18 +2061,18 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|–南</t>
+          <t xml:space="preserve">㴌|–姑</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-–南</t>
+          <t xml:space="preserve">㴌
+–姑</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">놀고낫거</t>
+          <t xml:space="preserve">높고</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2124,16 +2101,20 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|–南</t>
+          <t xml:space="preserve">姑|–南</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">姑
 –南</t>
         </is>
       </c>
-      <c r="I41" s="2"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">낮거</t>
+        </is>
+      </c>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2158,22 +2139,22 @@
       <c r="F42" s="2">
         <v>2</v>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 ) 요성</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
+      <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -2209,7 +2190,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새</t>
+          <t xml:space="preserve">내</t>
         </is>
       </c>
       <c r="J43" s="4"/>
@@ -2238,18 +2219,18 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–南</t>
+          <t xml:space="preserve">潢|–姑</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–南</t>
+–姑</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔을</t>
+          <t xml:space="preserve">팔</t>
         </is>
       </c>
       <c r="J44" s="4"/>
@@ -2429,7 +2410,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="58.2" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2444,24 +2425,24 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="58.2" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">춤</t>
         </is>
@@ -2471,7 +2452,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2481,97 +2462,98 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58.2" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">께</t>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-–</t>
-        </is>
-      </c>
-      <c r="E4" s="30"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="30"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I4" s="30"/>
-    </row>
-    <row r="5" ht="58.2" customHeight="1">
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58.2" customHeight="1">
+    <row r="6" ht="52.21" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-–南</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">놀
-고
-낫
-거</t>
+          <t xml:space="preserve">㴌
+–姑</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">높
+고</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -2579,7 +2561,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">덩</t>
         </is>
@@ -2589,10 +2571,9 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미
-야</t>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -2600,70 +2581,82 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58.2" customHeight="1">
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-–南</t>
-        </is>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-南</t>
-        </is>
-      </c>
-      <c r="E7" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">姑
 –南</t>
         </is>
       </c>
-      <c r="G7" s="30"/>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">낮
+거</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–南</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I7" s="30" t="inlineStr">
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="58.2" customHeight="1">
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C8" s="31"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G8" s="31" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2673,18 +2666,18 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="32"/>
-    </row>
-    <row r="9" ht="58.2" customHeight="1">
+      <c r="I8" s="26"/>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -2693,12 +2686,10 @@
 –潢</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내
-품
-안
-으</t>
+품</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -2707,11 +2698,10 @@
 –潢</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">산
-아
-지</t>
+아</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -2719,89 +2709,101 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="58.2" customHeight="1">
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–南</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">팔
-을</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+–姑</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
-      <c r="E10" s="29"/>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안
+으</t>
+        </is>
+      </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I10" s="29"/>
-    </row>
-    <row r="11" ht="58.2" customHeight="1">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I11" s="31"/>
-    </row>
-    <row r="12" ht="58.2" customHeight="1">
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I11" s="26"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -2812,7 +2814,7 @@
 –</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">들
 어</t>
@@ -2823,10 +2825,9 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구
-나</t>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -2834,20 +2835,20 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="58.2" customHeight="1">
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -2857,7 +2858,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -2867,40 +2868,44 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="30"/>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="58.2" customHeight="1">
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="32"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="32"/>
+      <c r="E14" s="26"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="32"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="32"/>
+      <c r="I14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -342,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -402,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -2217,23 +2217,27 @@
       <c r="F44" s="2">
         <v>3</v>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|–姑</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –姑</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">팔</t>
         </is>
       </c>
-      <c r="J44" s="4"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑/㴌?</t>
+        </is>
+      </c>
       <c r="K44" s="2"/>
     </row>
     <row r="45">
@@ -2717,13 +2721,13 @@
     </row>
     <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –姑</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">팔</t>
         </is>

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -418,10 +418,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -364,17 +364,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -491,7 +491,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -549,6 +549,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2460,322 +2504,322 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.01" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B3" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="11" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="24"/>
+      <c r="F5" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="24" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="11" t="s">
+      <c r="D7" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="11" t="s">
+      <c r="H7" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="23"/>
+      <c r="F8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="I8" s="23"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B9" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B10" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B11" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="13" t="s">
+      <c r="F11" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="I11" s="23"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B12" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="H12" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="11" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B13" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="11" t="s">
+      <c r="D13" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="11" t="s">
+      <c r="F13" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="11" t="s">
+      <c r="H13" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="12"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2783,7 +2827,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/전라도 산타령.xlsx
+++ b/sheets/민요/검수/전라도 산타령.xlsx
@@ -2510,13 +2510,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
